--- a/assets/worker_import_template.xlsx
+++ b/assets/worker_import_template.xlsx
@@ -130,7 +130,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -140,6 +140,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -483,8 +484,8 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.83203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.83203125" style="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13" style="5" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="34.33203125" style="3" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="20.83203125" style="1" bestFit="1" customWidth="1"/>
@@ -1258,9 +1259,24 @@
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D1048576" xr:uid="{00806D45-40E4-9D43-A65A-0F118AAB2C63}">
+  <dataValidations count="6">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="身份" prompt="请选择系统预设的身份。" sqref="D2:D1048576">
       <formula1>$K$4:$K$6</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="0" promptTitle="班组" prompt="请选择系统预设的班组。" sqref="E2:E1048576">
+      <formula1>"施工一队"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="0" promptTitle="证件类型" prompt="Excel 下拉不能多选。多个证件请手动输入，并用中文分号（；）分隔，例如：高压电工；高处。" sqref="F2:F1048576">
+      <formula1>"高压电工,低压电工,高处,电力电缆作业,电气试验,司索工,吊车司机,挖机操作工"</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="身份证号" error="请以文本填写18位身份证号，末位可为数字或X。" promptTitle="身份证号" prompt="请以文本填写18位身份证号，末位可为数字或X。" sqref="B2:B1048576">
+      <formula1>AND(LEN(B2)=18,ISTEXT(B2),SUMPRODUCT(--ISNUMBER(FIND(MID(B2,ROW($1:$17),1),"0123456789")))=17,ISNUMBER(FIND(RIGHT(B2,1),"0123456789Xx")))</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="电话号码" error="请以文本填写11位手机号。" promptTitle="电话号码" prompt="请以文本填写11位手机号。" sqref="C2:C1048576">
+      <formula1>AND(LEN(C2)=11,ISTEXT(C2),LEFT(C2,1)="1",SUMPRODUCT(--ISNUMBER(FIND(MID(C2,ROW($1:$11),1),"0123456789")))=11)</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="0" promptTitle="准入有效期" prompt="请填写完整日期范围：YYYY-MM-DD - YYYY-MM-DD，例如 2026-01-01 - 2026-12-31。" sqref="G2:G1048576">
+      <formula1>TRUE</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/assets/worker_import_template.xlsx
+++ b/assets/worker_import_template.xlsx
@@ -1263,11 +1263,11 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="身份" prompt="请选择系统预设的身份。" sqref="D2:D1048576">
       <formula1>$K$4:$K$6</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="0" promptTitle="班组" prompt="请选择系统预设的班组。" sqref="E2:E1048576">
-      <formula1>"施工一队"</formula1>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="0" promptTitle="班组" prompt="请填写本企业已有班组名称（与「设置 → 班组管理」里的名称一致）。" sqref="E2:E1048576">
+      <formula1>TRUE</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="0" promptTitle="证件类型" prompt="Excel 下拉不能多选。多个证件请手动输入，并用中文分号（；）分隔，例如：高压电工；高处。" sqref="F2:F1048576">
-      <formula1>"高压电工,低压电工,高处,电力电缆作业,电气试验,司索工,吊车司机,挖机操作工"</formula1>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="0" promptTitle="证件类型" prompt="多个证件请手动输入，并用中文分号（；）分隔，例如：高压电工；高处。" sqref="F2:F1048576">
+      <formula1>TRUE</formula1>
     </dataValidation>
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="身份证号" error="请以文本填写18位身份证号，末位可为数字或X。" promptTitle="身份证号" prompt="请以文本填写18位身份证号，末位可为数字或X。" sqref="B2:B1048576">
       <formula1>AND(LEN(B2)=18,ISTEXT(B2),SUMPRODUCT(--ISNUMBER(FIND(MID(B2,ROW($1:$17),1),"0123456789")))=17,ISNUMBER(FIND(RIGHT(B2,1),"0123456789Xx")))</formula1>
